--- a/award_forms/026_student_award_recommendation_form--award_forms.xlsx
+++ b/award_forms/026_student_award_recommendation_form--award_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Nominator Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Nominator Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Reviewer Comments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'award_recipients_option_1',_'value':_'first_name'}</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'award_recipients_option_1', 'value': 'First Name'}</t>
+          <t>First Name</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'award_recipients_option_2',_'value':_'last_name'}</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'award_recipients_option_2', 'value': 'Last Name'}</t>
+          <t>Last Name</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'award_recipients_option_3',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'award_recipients_option_3', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
